--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>222</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="D3">
-        <v>341</v>
+        <v>177</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D3">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>0</v>
